--- a/insurance_claim_forms/001_health_insurance_claim_form--insurance_claim_forms.xlsx
+++ b/insurance_claim_forms/001_health_insurance_claim_form--insurance_claim_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1003,8 +1003,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'inpatient'}</t>
+          <t>inpatient</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Inpatient'}</t>
+          <t>Inpatient</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'outpatient'}</t>
+          <t>outpatient</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Outpatient'}</t>
+          <t>Outpatient</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'urgent_care'}</t>
+          <t>urgent_care</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Urgent Care'}</t>
+          <t>Urgent Care</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'New'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'reopened'}</t>
+          <t>reopened</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Reopened'}</t>
+          <t>Reopened</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'gold'}</t>
+          <t>gold</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Gold'}</t>
+          <t>Gold</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'silver'}</t>
+          <t>silver</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Silver'}</t>
+          <t>Silver</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'bronze'}</t>
+          <t>bronze</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Bronze'}</t>
+          <t>Bronze</t>
         </is>
       </c>
     </row>
